--- a/objects/cancer_counts.xlsx
+++ b/objects/cancer_counts.xlsx
@@ -1358,7 +1358,9 @@
       <c r="B37" t="s">
         <v>74</v>
       </c>
-      <c r="C37"/>
+      <c r="C37" t="n">
+        <v>1177</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
@@ -1367,7 +1369,9 @@
       <c r="B38" t="s">
         <v>76</v>
       </c>
-      <c r="C38"/>
+      <c r="C38" t="n">
+        <v>1144</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
@@ -1376,7 +1380,9 @@
       <c r="B39" t="s">
         <v>78</v>
       </c>
-      <c r="C39"/>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
@@ -1396,7 +1402,9 @@
       <c r="B41" t="s">
         <v>82</v>
       </c>
-      <c r="C41"/>
+      <c r="C41" t="n">
+        <v>328</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
@@ -1405,7 +1413,9 @@
       <c r="B42" t="s">
         <v>84</v>
       </c>
-      <c r="C42"/>
+      <c r="C42" t="n">
+        <v>1281</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
@@ -1414,7 +1424,9 @@
       <c r="B43" t="s">
         <v>86</v>
       </c>
-      <c r="C43"/>
+      <c r="C43" t="n">
+        <v>193</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
@@ -1423,7 +1435,9 @@
       <c r="B44" t="s">
         <v>88</v>
       </c>
-      <c r="C44"/>
+      <c r="C44" t="n">
+        <v>1139</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
@@ -1432,7 +1446,9 @@
       <c r="B45" t="s">
         <v>90</v>
       </c>
-      <c r="C45"/>
+      <c r="C45" t="n">
+        <v>262</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
@@ -1441,7 +1457,9 @@
       <c r="B46" t="s">
         <v>92</v>
       </c>
-      <c r="C46"/>
+      <c r="C46" t="n">
+        <v>466</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
@@ -1450,7 +1468,9 @@
       <c r="B47" t="s">
         <v>94</v>
       </c>
-      <c r="C47"/>
+      <c r="C47" t="n">
+        <v>207</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
@@ -1459,7 +1479,9 @@
       <c r="B48" t="s">
         <v>96</v>
       </c>
-      <c r="C48"/>
+      <c r="C48" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
@@ -1468,7 +1490,9 @@
       <c r="B49" t="s">
         <v>98</v>
       </c>
-      <c r="C49"/>
+      <c r="C49" t="n">
+        <v>229</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
@@ -1477,7 +1501,9 @@
       <c r="B50" t="s">
         <v>100</v>
       </c>
-      <c r="C50"/>
+      <c r="C50" t="n">
+        <v>1058</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
@@ -1486,7 +1512,9 @@
       <c r="B51" t="s">
         <v>102</v>
       </c>
-      <c r="C51"/>
+      <c r="C51" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
@@ -1495,7 +1523,9 @@
       <c r="B52" t="s">
         <v>104</v>
       </c>
-      <c r="C52"/>
+      <c r="C52" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
@@ -1504,7 +1534,9 @@
       <c r="B53" t="s">
         <v>106</v>
       </c>
-      <c r="C53"/>
+      <c r="C53" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
@@ -1513,7 +1545,9 @@
       <c r="B54" t="s">
         <v>108</v>
       </c>
-      <c r="C54"/>
+      <c r="C54" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
